--- a/.schema/MHR_BUSHO.xlsx
+++ b/.schema/MHR_BUSHO.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7EBAA2-DE97-43FB-A885-51794F322CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2616EC01-7FE7-46BB-8532-46931885E626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16C90328-5CA8-4745-AEFC-BB3931E23911}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="14400" windowHeight="7800" xr2:uid="{16C90328-5CA8-4745-AEFC-BB3931E23911}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_BUSHO" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_BUSHO!$A$2:$I$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_BUSHO!$2:$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EMARF.MHR_BUSHO!$A$1:$I$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">EMARF.MHR_BUSHO!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>管理本部</t>
   </si>
@@ -61,9 +61,6 @@
     <t>TEKIYO_BI</t>
   </si>
   <si>
-    <t>OYA_BUSHO_ID</t>
-  </si>
-  <si>
     <t>BUSHO_MEI</t>
   </si>
   <si>
@@ -79,13 +76,314 @@
     <t>取締役会</t>
   </si>
   <si>
+    <t>営業本部</t>
+    <rPh sb="0" eb="2">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生産本部</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホンブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>総務部</t>
+    <rPh sb="0" eb="2">
+      <t>ソウム</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>人事部</t>
+    <rPh sb="0" eb="2">
+      <t>ジンジ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>経理部</t>
+    <rPh sb="0" eb="2">
+      <t>ケイリ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>情報システム部</t>
-  </si>
-  <si>
-    <t>情報システム課</t>
-  </si>
-  <si>
-    <t>情報システム係</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>東日本営業部</t>
+    <rPh sb="0" eb="1">
+      <t>ヒガシ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>西日本営業部</t>
+    <rPh sb="0" eb="1">
+      <t>ニシ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ニホン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>エイギョウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>製造部</t>
+    <rPh sb="0" eb="2">
+      <t>セイゾウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ブ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>人事課</t>
+    <rPh sb="0" eb="2">
+      <t>ジンジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>総務課</t>
+    <rPh sb="0" eb="2">
+      <t>ソウム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>経理課</t>
+    <rPh sb="0" eb="2">
+      <t>ケイリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>基盤課</t>
+    <rPh sb="0" eb="2">
+      <t>キバン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開発課</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>北海道営業課</t>
+  </si>
+  <si>
+    <t>東北営業課</t>
+  </si>
+  <si>
+    <t>関東営業課</t>
+  </si>
+  <si>
+    <t>中部営業課</t>
+  </si>
+  <si>
+    <t>近畿営業課</t>
+  </si>
+  <si>
+    <t>中国営業課</t>
+  </si>
+  <si>
+    <t>四国営業課</t>
+  </si>
+  <si>
+    <t>九州営業課</t>
+  </si>
+  <si>
+    <t>生産管理課</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生産技術課</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>購買課</t>
+    <rPh sb="0" eb="2">
+      <t>コウバイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物流課</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>人事係</t>
+    <rPh sb="0" eb="2">
+      <t>ジンジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>総務係</t>
+    <rPh sb="0" eb="2">
+      <t>ソウム</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>経理係</t>
+    <rPh sb="0" eb="2">
+      <t>ケイリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>基盤係</t>
+    <rPh sb="0" eb="2">
+      <t>キバン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>開発係</t>
+    <rPh sb="0" eb="2">
+      <t>カイハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>北海道営業係</t>
+  </si>
+  <si>
+    <t>東北営業係</t>
+  </si>
+  <si>
+    <t>関東営業係</t>
+  </si>
+  <si>
+    <t>中部営業係</t>
+  </si>
+  <si>
+    <t>近畿営業係</t>
+  </si>
+  <si>
+    <t>中国営業係</t>
+  </si>
+  <si>
+    <t>四国営業係</t>
+  </si>
+  <si>
+    <t>九州営業係</t>
+  </si>
+  <si>
+    <t>生産管理係</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>生産技術係</t>
+    <rPh sb="0" eb="2">
+      <t>セイサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ギジュツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>購買係</t>
+    <rPh sb="0" eb="2">
+      <t>コウバイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>物流係</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>P_BUSHO_ID</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -209,9 +507,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -249,7 +547,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -355,7 +653,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -497,7 +795,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -505,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF6BD59-F5E8-4D75-9D5D-2F54F818A4CD}">
-  <dimension ref="A2:I8"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.5" style="1" bestFit="1" customWidth="1"/>
@@ -518,59 +816,88 @@
     <col min="10" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>1</v>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="4" t="str">
+        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f t="shared" ref="H2:H47" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
+        <f t="shared" ref="A3:A47" si="1">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="4" t="str">
-        <f ca="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ref="F3:F47" ca="1" si="2">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="4" t="str">
-        <f t="shared" ref="H3:H8" ca="1" si="0">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -578,26 +905,27 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4" t="str">
-        <f t="shared" ref="F4:F8" ca="1" si="1">TEXT(NOW(),"yyyy/mm/dd hh:mm:ss")</f>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:53:37</v>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I4" s="2">
         <v>0</v>
@@ -605,10 +933,11 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -616,15 +945,15 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:53:37</v>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
@@ -632,26 +961,27 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:53:37</v>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
@@ -659,26 +989,27 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:53:37</v>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
@@ -686,33 +1017,1126 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="4" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>2026/08/16 10:53:37</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>2026/08/16 10:53:37</v>
+        <v>2026/10/21 10:17:39</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" s="2">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="2">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" s="2">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" s="2">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="2">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" s="2">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="2">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="2">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2">
+        <v>9</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="2">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3">
+        <v>10</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="2">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="3">
+        <v>10</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="2">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="3">
+        <v>10</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A22" s="2">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="3">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" s="2">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="3">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" s="2">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="3">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A25" s="2">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="3">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G25" s="2">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A26" s="2">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="3">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A27" s="2">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="3">
+        <v>12</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G27" s="2">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I27" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A28" s="2">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="3">
+        <v>12</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0</v>
+      </c>
+      <c r="H28" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I28" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A29" s="2">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3">
+        <v>12</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A30" s="2">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="3">
+        <v>12</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0</v>
+      </c>
+      <c r="H30" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A31" s="2">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G31" s="2">
+        <v>0</v>
+      </c>
+      <c r="H31" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I31" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A32" s="2">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="2">
+        <v>14</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G32" s="2">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" s="2">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="2">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0</v>
+      </c>
+      <c r="H33" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" s="2">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="2">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G34" s="2">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" s="2">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="2">
+        <v>17</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G35" s="2">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" s="2">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C36" s="3">
+        <v>18</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G36" s="2">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" s="2">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="3">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" s="2">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="3">
+        <v>20</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0</v>
+      </c>
+      <c r="H38" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" s="2">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="3">
+        <v>21</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G39" s="2">
+        <v>0</v>
+      </c>
+      <c r="H39" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" s="2">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="3">
+        <v>22</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G40" s="2">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" s="2">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="3">
+        <v>23</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G41" s="2">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I41" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" s="2">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="3">
+        <v>24</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G42" s="2">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" s="2">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="3">
+        <v>25</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A44" s="2">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="3">
+        <v>26</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G44" s="2">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I44" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A45" s="2">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="3">
+        <v>27</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G45" s="2">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I45" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A46" s="2">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="3">
+        <v>28</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G46" s="2">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I46" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A47" s="2">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47" s="3">
+        <v>29</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="4" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="G47" s="2">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v>2026/10/21 10:17:39</v>
+      </c>
+      <c r="I47" s="2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I8" xr:uid="{93FB77D7-EEC8-48FA-AF85-D99D54D71BED}"/>
+  <autoFilter ref="A1:I9" xr:uid="{93FB77D7-EEC8-48FA-AF85-D99D54D71BED}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
